--- a/lang/pt/headTags.xlsx
+++ b/lang/pt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2061">
   <si>
     <t>en</t>
   </si>
@@ -5005,6 +5005,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Inspirado)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (Baunilha)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5800,6 +5812,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6062,6 +6077,12 @@
   </si>
   <si>
     <t>inverno</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Coleção de Inverno</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6525,7 +6546,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14233,36 +14254,36 @@
         <v>1662</v>
       </c>
       <c r="B963" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B964" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B965" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B966" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B967" t="s">
         <v>1668</v>
@@ -14289,28 +14310,28 @@
         <v>1673</v>
       </c>
       <c r="B970" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B971" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="B972" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B973" t="s">
         <v>1678</v>
@@ -14361,28 +14382,28 @@
         <v>1689</v>
       </c>
       <c r="B979" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B980" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="B981" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B982" t="s">
         <v>1694</v>
@@ -14393,20 +14414,20 @@
         <v>1695</v>
       </c>
       <c r="B983" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B984" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B985" t="s">
         <v>1699</v>
@@ -14481,20 +14502,20 @@
         <v>1716</v>
       </c>
       <c r="B994" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B995" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B996" t="s">
         <v>1720</v>
@@ -14521,28 +14542,28 @@
         <v>1725</v>
       </c>
       <c r="B999" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1000" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B1001" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1002" t="s">
         <v>1730</v>
@@ -14561,20 +14582,20 @@
         <v>1733</v>
       </c>
       <c r="B1004" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1005" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1006" t="s">
         <v>1737</v>
@@ -14585,20 +14606,20 @@
         <v>1738</v>
       </c>
       <c r="B1007" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1008" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1009" t="s">
         <v>1742</v>
@@ -14665,36 +14686,36 @@
         <v>1757</v>
       </c>
       <c r="B1017" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1018" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="B1019" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B1020" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B1021" t="s">
         <v>1763</v>
@@ -14705,36 +14726,36 @@
         <v>1764</v>
       </c>
       <c r="B1022" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B1023" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="B1024" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B1025" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1026" t="s">
         <v>1770</v>
@@ -14753,44 +14774,44 @@
         <v>1773</v>
       </c>
       <c r="B1028" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1029" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1030" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1031" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B1032" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1033" t="s">
         <v>1781</v>
@@ -14801,20 +14822,20 @@
         <v>1782</v>
       </c>
       <c r="B1034" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1035" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1036" t="s">
         <v>1786</v>
@@ -14833,100 +14854,100 @@
         <v>1789</v>
       </c>
       <c r="B1038" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1039" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1040" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1041" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B1042" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1043" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1044" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="B1045" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="B1046" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B1047" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1048" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1049" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1050" t="s">
         <v>1806</v>
@@ -14937,20 +14958,20 @@
         <v>1807</v>
       </c>
       <c r="B1051" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1052" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1053" t="s">
         <v>1811</v>
@@ -14969,20 +14990,20 @@
         <v>1814</v>
       </c>
       <c r="B1055" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1056" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1057" t="s">
         <v>1818</v>
@@ -15025,20 +15046,20 @@
         <v>1827</v>
       </c>
       <c r="B1062" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1063" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1064" t="s">
         <v>1831</v>
@@ -15121,20 +15142,20 @@
         <v>1850</v>
       </c>
       <c r="B1074" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1075" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1076" t="s">
         <v>1854</v>
@@ -15217,28 +15238,28 @@
         <v>1873</v>
       </c>
       <c r="B1086" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1087" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="B1088" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1089" t="s">
         <v>1878</v>
@@ -15257,44 +15278,44 @@
         <v>1881</v>
       </c>
       <c r="B1091" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1092" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="B1093" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B1094" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B1095" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B1096" t="s">
         <v>1889</v>
@@ -15305,20 +15326,20 @@
         <v>1890</v>
       </c>
       <c r="B1097" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1098" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1099" t="s">
         <v>1894</v>
@@ -15337,20 +15358,20 @@
         <v>1897</v>
       </c>
       <c r="B1101" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1102" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1103" t="s">
         <v>1901</v>
@@ -15385,20 +15406,20 @@
         <v>1908</v>
       </c>
       <c r="B1107" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1108" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1109" t="s">
         <v>1912</v>
@@ -15433,20 +15454,20 @@
         <v>1919</v>
       </c>
       <c r="B1113" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1114" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1115" t="s">
         <v>1923</v>
@@ -15465,44 +15486,44 @@
         <v>1926</v>
       </c>
       <c r="B1117" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1118" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1119" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1120" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1121" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1122" t="s">
         <v>1934</v>
@@ -15513,84 +15534,84 @@
         <v>1935</v>
       </c>
       <c r="B1123" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1937</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1939</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1949</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B1133" t="s">
         <v>1955</v>
@@ -15617,12 +15638,12 @@
         <v>1960</v>
       </c>
       <c r="B1136" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B1137" t="s">
         <v>1962</v>
@@ -15649,60 +15670,60 @@
         <v>1967</v>
       </c>
       <c r="B1140" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1969</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1970</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1971</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1972</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1973</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1974</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1975</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1977</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1979</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B1147" t="s">
         <v>1981</v>
@@ -15713,44 +15734,44 @@
         <v>1982</v>
       </c>
       <c r="B1148" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1149" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B1150" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B1151" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B1152" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1153" t="s">
         <v>1989</v>
@@ -15769,20 +15790,20 @@
         <v>1991</v>
       </c>
       <c r="B1155" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1156" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1157" t="s">
         <v>1995</v>
@@ -15793,68 +15814,68 @@
         <v>1996</v>
       </c>
       <c r="B1158" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1159" t="s">
         <v>1998</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>1999</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1160" t="s">
         <v>2000</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>2001</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1161" t="s">
         <v>2002</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>2003</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1162" t="s">
         <v>2004</v>
-      </c>
-      <c r="B1162" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1163" t="s">
         <v>2006</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1164" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1165" t="s">
         <v>2010</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B1166" t="s">
         <v>2012</v>
@@ -15873,12 +15894,12 @@
         <v>2015</v>
       </c>
       <c r="B1168" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B1169" t="s">
         <v>2017</v>
@@ -15905,12 +15926,12 @@
         <v>2022</v>
       </c>
       <c r="B1172" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B1173" t="s">
         <v>2024</v>
@@ -15921,132 +15942,132 @@
         <v>2025</v>
       </c>
       <c r="B1174" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B1175" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="B1176" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B1177" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B1178" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="B1179" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1180" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1181" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1182" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B1183" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="B1184" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="B1185" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="B1186" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B1187" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B1188" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B1189" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B1190" t="s">
         <v>2047</v>
@@ -16057,35 +16078,67 @@
         <v>2048</v>
       </c>
       <c r="B1191" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B1192" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B1193" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1194" t="s">
-        <v>2053</v>
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2060</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
